--- a/apps/cliente/public/examples/file_payroll.xlsx
+++ b/apps/cliente/public/examples/file_payroll.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="32">
   <si>
     <t>employee_code</t>
   </si>
@@ -83,6 +83,30 @@
   </si>
   <si>
     <t>absence_deduction</t>
+  </si>
+  <si>
+    <t>EMP004</t>
+  </si>
+  <si>
+    <t>EMP005</t>
+  </si>
+  <si>
+    <t>EMP006</t>
+  </si>
+  <si>
+    <t>EMP007</t>
+  </si>
+  <si>
+    <t>EMP008</t>
+  </si>
+  <si>
+    <t>EMP009</t>
+  </si>
+  <si>
+    <t>EMP010</t>
+  </si>
+  <si>
+    <t>EMP011</t>
   </si>
 </sst>
 </file>
@@ -101,17 +125,12 @@
       <b/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -128,7 +147,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,16 +487,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -614,7 +632,7 @@
         <v>15</v>
       </c>
       <c r="H5">
-        <v>210000</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -641,6 +659,301 @@
       </c>
       <c r="H6">
         <v>-5250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8">
+        <v>9000</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>245000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11">
+        <v>275000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12">
+        <v>10500</v>
+      </c>
+      <c r="I12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13">
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14">
+        <v>305000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16">
+        <v>12000</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17">
+        <v>335000</v>
       </c>
     </row>
   </sheetData>
